--- a/Super Smash Bros Remix-FrameData (version 1.5).xlsx
+++ b/Super Smash Bros Remix-FrameData (version 1.5).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Neros\webside\(SSR) Frame Data\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668552C0-36F8-489F-BE39-8163E73771AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A664B2-AF8A-426F-84B5-F49420CED0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="887" firstSheet="33" activeTab="42" xr2:uid="{3300E2F6-31EA-4A47-BF19-C0FAB0E99017}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="887" xr2:uid="{3300E2F6-31EA-4A47-BF19-C0FAB0E99017}"/>
   </bookViews>
   <sheets>
     <sheet name="marina" sheetId="13" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3719" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3762" uniqueCount="974">
   <si>
     <t>Luigi_OG</t>
   </si>
@@ -2971,6 +2971,60 @@
   </si>
   <si>
     <t>U-Special(Health-Air)</t>
+  </si>
+  <si>
+    <t>11%-8%</t>
+  </si>
+  <si>
+    <t>Legs intangibility on frames 1-8</t>
+  </si>
+  <si>
+    <t>Head Intangibility on frames 6-13</t>
+  </si>
+  <si>
+    <t>Grab an enemy and set a direction for different move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body intangibility on frames 6-24 (The first "UpThrow" on SSB 64) </t>
+  </si>
+  <si>
+    <t>Body intangibility on frames 6-39 (The first "DownThrow" on SSB 64)</t>
+  </si>
+  <si>
+    <t>Body intangibility on frames 6-25</t>
+  </si>
+  <si>
+    <t>16%-9%</t>
+  </si>
+  <si>
+    <t>On frame 8, you can absorb projectiles</t>
+  </si>
+  <si>
+    <t>If you don't have anything, then good luck</t>
+  </si>
+  <si>
+    <t>19…</t>
+  </si>
+  <si>
+    <t>Depending on how many projectiles you absorb, you will obtain something.</t>
+  </si>
+  <si>
+    <t>Pressing DownB and press B again</t>
+  </si>
+  <si>
+    <t>Each thing has it's own properties</t>
+  </si>
+  <si>
+    <t>15%-7%</t>
+  </si>
+  <si>
+    <t>15%-9%</t>
+  </si>
+  <si>
+    <t>12%-5%</t>
+  </si>
+  <si>
+    <t>This move have 2 blows</t>
   </si>
 </sst>
 </file>
@@ -3377,7 +3431,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -3494,6 +3548,17 @@
     <xf numFmtId="0" fontId="0" fillId="57" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3856,6 +3921,7 @@
     <col min="7" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="68.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3954,6 +4020,9 @@
       <c r="J4" s="8">
         <v>0.03</v>
       </c>
+      <c r="K4" s="95" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="47" t="s">
@@ -3986,6 +4055,9 @@
       <c r="J5" s="8">
         <v>0.03</v>
       </c>
+      <c r="K5" s="95" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="47" t="s">
@@ -4017,6 +4089,9 @@
       </c>
       <c r="J6" s="8">
         <v>0.01</v>
+      </c>
+      <c r="K6" s="95" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -4062,7 +4137,12 @@
       <c r="I8" s="3">
         <v>21</v>
       </c>
-      <c r="J8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K8" s="95" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="47" t="s">
@@ -4092,7 +4172,12 @@
       <c r="I9" s="3">
         <v>24</v>
       </c>
-      <c r="J9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="96" t="s">
+        <v>958</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="47" t="s">
@@ -4122,7 +4207,12 @@
       <c r="I10" s="3">
         <v>22</v>
       </c>
-      <c r="J10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="K10" s="95" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
@@ -4152,7 +4242,12 @@
       <c r="I11" s="3">
         <v>24</v>
       </c>
-      <c r="J11" s="3"/>
+      <c r="J11" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K11" s="95" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
@@ -4197,7 +4292,12 @@
       <c r="I13" s="3">
         <v>30</v>
       </c>
-      <c r="J13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" s="96" t="s">
+        <v>957</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="47" t="s">
@@ -4227,7 +4327,12 @@
       <c r="I14" s="3">
         <v>34</v>
       </c>
-      <c r="J14" s="3"/>
+      <c r="J14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K14" s="95" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="47" t="s">
@@ -4257,7 +4362,12 @@
       <c r="I15" s="3">
         <v>34</v>
       </c>
-      <c r="J15" s="3"/>
+      <c r="J15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="95" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
@@ -4302,7 +4412,12 @@
       <c r="I17" s="3">
         <v>0</v>
       </c>
-      <c r="J17" s="8"/>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>959</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="47" t="s">
@@ -4332,7 +4447,12 @@
       <c r="I18" s="3">
         <v>0</v>
       </c>
-      <c r="J18" s="8"/>
+      <c r="J18" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K18" t="s">
+        <v>960</v>
+      </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="47" t="s">
@@ -4362,7 +4482,12 @@
       <c r="I19" s="3">
         <v>0</v>
       </c>
-      <c r="J19" s="8"/>
+      <c r="J19" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K19" t="s">
+        <v>961</v>
+      </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="47" t="s">
@@ -4392,7 +4517,12 @@
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3"/>
+      <c r="J20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" t="s">
+        <v>962</v>
+      </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="47" t="s">
@@ -4422,7 +4552,12 @@
       <c r="I21" s="3">
         <v>30</v>
       </c>
-      <c r="J21" s="3"/>
+      <c r="J21" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="K21" s="95" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="47" t="s">
@@ -4452,7 +4587,12 @@
       <c r="I22" s="3">
         <v>24</v>
       </c>
-      <c r="J22" s="3"/>
+      <c r="J22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" t="s">
+        <v>964</v>
+      </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="47" t="s">
@@ -4485,6 +4625,9 @@
       <c r="J23" s="8">
         <v>0</v>
       </c>
+      <c r="K23" t="s">
+        <v>965</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="47" t="s">
@@ -4502,8 +4645,8 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3">
-        <v>19</v>
+      <c r="F24" s="3" t="s">
+        <v>966</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -4516,6 +4659,9 @@
       </c>
       <c r="J24" s="8">
         <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -4549,6 +4695,9 @@
       <c r="J25" s="8">
         <v>0</v>
       </c>
+      <c r="K25" t="s">
+        <v>968</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="47" t="s">
@@ -4580,6 +4729,9 @@
       </c>
       <c r="J26" s="94" t="s">
         <v>808</v>
+      </c>
+      <c r="K26" s="97" t="s">
+        <v>969</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -4628,6 +4780,9 @@
       <c r="J28" s="8">
         <v>0.1</v>
       </c>
+      <c r="K28" s="95" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="47" t="s">
@@ -4660,6 +4815,9 @@
       <c r="J29" s="8">
         <v>0.13</v>
       </c>
+      <c r="K29" s="95" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="47" t="s">
@@ -4692,6 +4850,9 @@
       <c r="J30" s="8">
         <v>0.16</v>
       </c>
+      <c r="K30" s="99" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="47" t="s">
@@ -4724,6 +4885,9 @@
       <c r="J31" s="8">
         <v>0.09</v>
       </c>
+      <c r="K31" s="95" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="47" t="s">
@@ -4755,6 +4919,9 @@
       </c>
       <c r="J32" s="8" t="s">
         <v>350</v>
+      </c>
+      <c r="K32" s="95" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -4800,7 +4967,9 @@
       <c r="I34" s="3">
         <v>29</v>
       </c>
-      <c r="J34" s="3"/>
+      <c r="J34" s="3" t="s">
+        <v>970</v>
+      </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="47" t="s">
@@ -4830,7 +4999,9 @@
       <c r="I35" s="3">
         <v>29</v>
       </c>
-      <c r="J35" s="3"/>
+      <c r="J35" s="3" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="47" t="s">
@@ -4860,7 +5031,9 @@
       <c r="I36" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="J36" s="3"/>
+      <c r="J36" s="8">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="47" t="s">
@@ -4890,7 +5063,12 @@
       <c r="I37" s="3" t="s">
         <v>737</v>
       </c>
-      <c r="J37" s="3"/>
+      <c r="J37" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="K37" s="98" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="47" t="s">
@@ -4920,7 +5098,9 @@
       <c r="I38" s="3">
         <v>30</v>
       </c>
-      <c r="J38" s="3"/>
+      <c r="J38" s="3" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
@@ -25398,7 +25578,7 @@
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
+      <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -25407,10 +25587,9 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
+      <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -25419,10 +25598,9 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
+      <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -25431,7 +25609,6 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Super Smash Bros Remix-FrameData (version 1.5).xlsx
+++ b/Super Smash Bros Remix-FrameData (version 1.5).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Neros\webside\(SSR) Frame Data\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A664B2-AF8A-426F-84B5-F49420CED0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78574D47-6CE3-4F2A-9971-B5FD00142FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="887" xr2:uid="{3300E2F6-31EA-4A47-BF19-C0FAB0E99017}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="887" activeTab="14" xr2:uid="{3300E2F6-31EA-4A47-BF19-C0FAB0E99017}"/>
   </bookViews>
   <sheets>
     <sheet name="marina" sheetId="13" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3762" uniqueCount="974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4305" uniqueCount="1104">
   <si>
     <t>Luigi_OG</t>
   </si>
@@ -3024,14 +3024,404 @@
     <t>12%-5%</t>
   </si>
   <si>
-    <t>This move have 2 blows</t>
+    <t>On frame 16, a BlueGem appears by shaking an enemy</t>
+  </si>
+  <si>
+    <t>11%-9%</t>
+  </si>
+  <si>
+    <t>19%-15%</t>
+  </si>
+  <si>
+    <t>Head intangibility on frames 7-10</t>
+  </si>
+  <si>
+    <t>12%-15%</t>
+  </si>
+  <si>
+    <t>The movement has electricity.</t>
+  </si>
+  <si>
+    <t>23%-1%</t>
+  </si>
+  <si>
+    <t>Body intagibility on frames 1-2</t>
+  </si>
+  <si>
+    <t>It's not a multi-hit like mario</t>
+  </si>
+  <si>
+    <t>Megavitamins</t>
+  </si>
+  <si>
+    <t>12%-7%</t>
+  </si>
+  <si>
+    <t>14%-8%</t>
+  </si>
+  <si>
+    <t>Every hit deals 2% of damage</t>
+  </si>
+  <si>
+    <t>Head Intangibility on frames 7-10</t>
+  </si>
+  <si>
+    <t>18%-12%</t>
+  </si>
+  <si>
+    <t>deals more damage on ground that in air.</t>
+  </si>
+  <si>
+    <t>Body intangibility on frame 2, and on frame 2 luigi can deal a powerfull strike</t>
+  </si>
+  <si>
+    <t>6%-5%</t>
+  </si>
+  <si>
+    <t>FIREBALL!!!</t>
+  </si>
+  <si>
+    <t>14%-9%</t>
+  </si>
+  <si>
+    <t>16%-8%</t>
+  </si>
+  <si>
+    <t>16%-10%</t>
+  </si>
+  <si>
+    <t>12%-8%</t>
+  </si>
+  <si>
+    <t>5%-1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Hit, you are steeling money </t>
+  </si>
+  <si>
+    <t>12%-16%</t>
+  </si>
+  <si>
+    <t>20%-15%</t>
+  </si>
+  <si>
+    <t>Loading animation hit</t>
+  </si>
+  <si>
+    <t>body intangibility on frames 23-24, powerfull blow</t>
+  </si>
+  <si>
+    <t>12%-3%</t>
+  </si>
+  <si>
+    <t>body intangibility on frames 1-5, poor up-b</t>
+  </si>
+  <si>
+    <t>10%-5%</t>
+  </si>
+  <si>
+    <t>body intangibility on frames 1-2.</t>
+  </si>
+  <si>
+    <t>13%-8%</t>
+  </si>
+  <si>
+    <t>18%-13%</t>
+  </si>
+  <si>
+    <t>Explosive bomb</t>
+  </si>
+  <si>
+    <t>10%-6%</t>
+  </si>
+  <si>
+    <t>20%-9%</t>
+  </si>
+  <si>
+    <t>5 blows with the same damage</t>
+  </si>
+  <si>
+    <t>7 stages for complete the load</t>
+  </si>
+  <si>
+    <t>2%-1%</t>
+  </si>
+  <si>
+    <t>deals more damage in ground that air</t>
+  </si>
+  <si>
+    <t>Explotion occurs one  frame after touching a target. Bomb explodes automatically on frame 110.</t>
+  </si>
+  <si>
+    <t>5%-4%</t>
+  </si>
+  <si>
+    <t>14%-7%</t>
+  </si>
+  <si>
+    <t>2 blows</t>
+  </si>
+  <si>
+    <t>this hit is fire!</t>
+  </si>
+  <si>
+    <t>24%-18%</t>
+  </si>
+  <si>
+    <t>FALCON-PUNCH!!!</t>
+  </si>
+  <si>
+    <t>59 frames of endlag when is successful</t>
+  </si>
+  <si>
+    <t>Don't recommended if the enemy is on low percent</t>
+  </si>
+  <si>
+    <t>This jab electrify the enemy</t>
+  </si>
+  <si>
+    <t>22%-17%</t>
+  </si>
+  <si>
+    <t>A really good hit, it's like a "BOMB"</t>
+  </si>
+  <si>
+    <t>15%-8%</t>
+  </si>
+  <si>
+    <t>2 blows and big damage</t>
+  </si>
+  <si>
+    <t>31%-24%</t>
+  </si>
+  <si>
+    <t>This POWERFUL STRIKE have A LOT of armor</t>
+  </si>
+  <si>
+    <t>Body intangibility on frames 4-14.</t>
+  </si>
+  <si>
+    <t>Landing hit on frame 1</t>
+  </si>
+  <si>
+    <t>68 frames if you are on air after been in ground</t>
+  </si>
+  <si>
+    <t>12%-6%</t>
+  </si>
+  <si>
+    <t>16%-2%</t>
+  </si>
+  <si>
+    <t>GO!!!</t>
+  </si>
+  <si>
+    <t>Get Ready?</t>
+  </si>
+  <si>
+    <t>The most OP recovery on smash remix</t>
+  </si>
+  <si>
+    <t>It's better bounce than land</t>
+  </si>
+  <si>
+    <t>49 frames of endlag on hit</t>
+  </si>
+  <si>
+    <t>13%-2%</t>
+  </si>
+  <si>
+    <t>/*Please, wait for a new update*/</t>
+  </si>
+  <si>
+    <t>/*Please, wait for a new update*/, Multi-Hit, 9 hit in a row</t>
+  </si>
+  <si>
+    <t>/*Please, wait for a new update*/, This move have 2 blows</t>
+  </si>
+  <si>
+    <t>/*Please, wait for a new update*/, Every hit deals 3% of damage</t>
+  </si>
+  <si>
+    <t>/*Please, wait for a new update*/, 5 blows with the same damage</t>
+  </si>
+  <si>
+    <t>Body intangibility on frames 13-53, but on frames 44-81 sonic can get hit.</t>
+  </si>
+  <si>
+    <t>Do a barrel roll</t>
+  </si>
+  <si>
+    <t>Head intangibility on frames 6-9</t>
+  </si>
+  <si>
+    <t>19%-13%</t>
+  </si>
+  <si>
+    <t>17%-8%</t>
+  </si>
+  <si>
+    <t>You can suck projectiles, and your own projectiles too</t>
+  </si>
+  <si>
+    <t>(50/30)</t>
+  </si>
+  <si>
+    <t>On frame 10-14 is invincible and gets a Super Armor. Head intangibility on frames 15-25. On frame 51…(until you land) legs are intangible. Cancelling incurs 30 frames landinglag. Landing hitbox on frame 1-3. Stars appears on frame 4-18.</t>
+  </si>
+  <si>
+    <t>Helpers(Waddle Dee, Waddle Doo, Gordo)</t>
+  </si>
+  <si>
+    <t>491/491/231</t>
+  </si>
+  <si>
+    <t>(6/6/11)</t>
+  </si>
+  <si>
+    <t>(9/9/34)</t>
+  </si>
+  <si>
+    <t>This MF can deals 54% easy. Every flash are 2 hits. Hits 24 blows.</t>
+  </si>
+  <si>
+    <t>Just and hits.</t>
+  </si>
+  <si>
+    <t>Sticks to the floor or at the corners of stages.</t>
+  </si>
+  <si>
+    <t>3%/3%/18%</t>
+  </si>
+  <si>
+    <t>Just and hits. / Can deals 54% easy. Every flash are 2 hits. Hits 24 blows. / Sticks to the floor or at the corners of stages.</t>
+  </si>
+  <si>
+    <t>8%-2%</t>
+  </si>
+  <si>
+    <t>/*Please, wait for a new update*/. Head intangibility on frames 1-40</t>
+  </si>
+  <si>
+    <t>Really fast moves</t>
+  </si>
+  <si>
+    <t>If you go forward and B at the same time the boomerang will go more further</t>
+  </si>
+  <si>
+    <t>9%-1%</t>
+  </si>
+  <si>
+    <t>The last hit deals 9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This bomb can run (only forward), you can throw it more further if you stick forward and press A at the same time. </t>
+  </si>
+  <si>
+    <t>13%-7%</t>
+  </si>
+  <si>
+    <t>18%-8%</t>
+  </si>
+  <si>
+    <t>/*Please, wait for a new update*/, if you hit the enemy once you can wait for the second hitbox appears on 30 frames later</t>
+  </si>
+  <si>
+    <t>Head intangibility on frames 5-19</t>
+  </si>
+  <si>
+    <t>That yoyo it's going on!</t>
+  </si>
+  <si>
+    <t>That yoyo it's really hard</t>
+  </si>
+  <si>
+    <t>You can reflect attacks</t>
+  </si>
+  <si>
+    <t>heals 2.0x damage if an energy or electric projectile hits it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you hit someone </t>
+  </si>
+  <si>
+    <t>body intangibility on frames 1-9</t>
+  </si>
+  <si>
+    <t>30%-23%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">body intangibility on frames 1-9 </t>
+  </si>
+  <si>
+    <t>4%-3%</t>
+  </si>
+  <si>
+    <t>Will not erupt on shields. The flame pilar has a rehit rate of 11 and lasts about 101 frames.</t>
+  </si>
+  <si>
+    <t>/*Please, wait for a new update*/. Auto-Cancel his self</t>
+  </si>
+  <si>
+    <t>/*Please, wait for a new update*/. Head intangibility on frames 8-11. Auto-Cancel his self</t>
+  </si>
+  <si>
+    <t>Chaingrab</t>
+  </si>
+  <si>
+    <t>If you hit your joystick any direcction and press A at the same time the bomb can go more further.</t>
+  </si>
+  <si>
+    <t>Young link doesn't have chaingrab like link does</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes: </t>
+  </si>
+  <si>
+    <t>head intangibility on frames 7-10</t>
+  </si>
+  <si>
+    <t>Head and foreamrs intangiblity on frames 14-18</t>
+  </si>
+  <si>
+    <t>head intangibility on frames 1-12</t>
+  </si>
+  <si>
+    <t>head intangibility on frames 6-15</t>
+  </si>
+  <si>
+    <t>head intangibility on frames 6-24</t>
+  </si>
+  <si>
+    <t>swipes the floor with his/its tail</t>
+  </si>
+  <si>
+    <t>82, --</t>
+  </si>
+  <si>
+    <t>The total frames assumes level ground. Stars appears on frame 4 of landing</t>
+  </si>
+  <si>
+    <t>eggs explodes automatically on frame 50</t>
+  </si>
+  <si>
+    <t>a better option that grab</t>
+  </si>
+  <si>
+    <t>Depending on how hard you press buttons, the egg will emerge soon or not.</t>
+  </si>
+  <si>
+    <t>/*Please, wait for a new update*/. A powerfull spike</t>
+  </si>
+  <si>
+    <t>They appears on frame 4 and vanish on frame 18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3070,6 +3460,25 @@
     <font>
       <sz val="11"/>
       <color theme="2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3431,7 +3840,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -3549,8 +3958,6 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3558,6 +3965,32 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3955,7 +4388,7 @@
       <c r="J1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="98" t="s">
         <v>800</v>
       </c>
     </row>
@@ -3972,7 +4405,7 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
+      <c r="K2" s="99"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
@@ -3987,7 +4420,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
+      <c r="K3" s="100"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="47" t="s">
@@ -4020,7 +4453,7 @@
       <c r="J4" s="8">
         <v>0.03</v>
       </c>
-      <c r="K4" s="95" t="s">
+      <c r="K4" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4055,7 +4488,7 @@
       <c r="J5" s="8">
         <v>0.03</v>
       </c>
-      <c r="K5" s="95" t="s">
+      <c r="K5" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4090,7 +4523,7 @@
       <c r="J6" s="8">
         <v>0.01</v>
       </c>
-      <c r="K6" s="95" t="s">
+      <c r="K6" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4107,7 +4540,7 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="K7" s="100"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
@@ -4140,7 +4573,7 @@
       <c r="J8" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="K8" s="95" t="s">
+      <c r="K8" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4175,7 +4608,7 @@
       <c r="J9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="K9" s="96" t="s">
+      <c r="K9" s="101" t="s">
         <v>958</v>
       </c>
     </row>
@@ -4210,7 +4643,7 @@
       <c r="J10" s="3" t="s">
         <v>956</v>
       </c>
-      <c r="K10" s="95" t="s">
+      <c r="K10" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4245,7 +4678,7 @@
       <c r="J11" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="K11" s="95" t="s">
+      <c r="K11" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4262,7 +4695,7 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="100"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="47" t="s">
@@ -4295,7 +4728,7 @@
       <c r="J13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K13" s="96" t="s">
+      <c r="K13" s="101" t="s">
         <v>957</v>
       </c>
     </row>
@@ -4330,7 +4763,7 @@
       <c r="J14" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="K14" s="95" t="s">
+      <c r="K14" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4365,7 +4798,7 @@
       <c r="J15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="K15" s="95" t="s">
+      <c r="K15" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4382,7 +4815,7 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="K16" s="100"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="47" t="s">
@@ -4415,7 +4848,7 @@
       <c r="J17" s="8">
         <v>0</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="96" t="s">
         <v>959</v>
       </c>
     </row>
@@ -4450,7 +4883,7 @@
       <c r="J18" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="96" t="s">
         <v>960</v>
       </c>
     </row>
@@ -4485,7 +4918,7 @@
       <c r="J19" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="96" t="s">
         <v>961</v>
       </c>
     </row>
@@ -4520,7 +4953,7 @@
       <c r="J20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="96" t="s">
         <v>962</v>
       </c>
     </row>
@@ -4555,7 +4988,7 @@
       <c r="J21" s="3" t="s">
         <v>963</v>
       </c>
-      <c r="K21" s="95" t="s">
+      <c r="K21" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4590,7 +5023,7 @@
       <c r="J22" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" s="96" t="s">
         <v>964</v>
       </c>
     </row>
@@ -4625,7 +5058,7 @@
       <c r="J23" s="8">
         <v>0</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="96" t="s">
         <v>965</v>
       </c>
     </row>
@@ -4660,7 +5093,7 @@
       <c r="J24" s="8">
         <v>0</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" s="96" t="s">
         <v>967</v>
       </c>
     </row>
@@ -4695,7 +5128,7 @@
       <c r="J25" s="8">
         <v>0</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K25" s="96" t="s">
         <v>968</v>
       </c>
     </row>
@@ -4730,7 +5163,7 @@
       <c r="J26" s="94" t="s">
         <v>808</v>
       </c>
-      <c r="K26" s="97" t="s">
+      <c r="K26" s="95" t="s">
         <v>969</v>
       </c>
     </row>
@@ -4747,7 +5180,7 @@
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
+      <c r="K27" s="100"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="47" t="s">
@@ -4780,7 +5213,7 @@
       <c r="J28" s="8">
         <v>0.1</v>
       </c>
-      <c r="K28" s="95" t="s">
+      <c r="K28" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4815,7 +5248,7 @@
       <c r="J29" s="8">
         <v>0.13</v>
       </c>
-      <c r="K29" s="95" t="s">
+      <c r="K29" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4850,7 +5283,7 @@
       <c r="J30" s="8">
         <v>0.16</v>
       </c>
-      <c r="K30" s="99" t="s">
+      <c r="K30" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4885,7 +5318,7 @@
       <c r="J31" s="8">
         <v>0.09</v>
       </c>
-      <c r="K31" s="95" t="s">
+      <c r="K31" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4920,7 +5353,7 @@
       <c r="J32" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="K32" s="95" t="s">
+      <c r="K32" s="97" t="s">
         <v>613</v>
       </c>
     </row>
@@ -4937,7 +5370,7 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
+      <c r="K33" s="100"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="47" t="s">
@@ -4970,6 +5403,9 @@
       <c r="J34" s="3" t="s">
         <v>970</v>
       </c>
+      <c r="K34" s="97" t="s">
+        <v>1042</v>
+      </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="47" t="s">
@@ -5002,6 +5438,9 @@
       <c r="J35" s="3" t="s">
         <v>971</v>
       </c>
+      <c r="K35" s="97" t="s">
+        <v>1042</v>
+      </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="47" t="s">
@@ -5034,6 +5473,9 @@
       <c r="J36" s="8">
         <v>0.03</v>
       </c>
+      <c r="K36" s="96" t="s">
+        <v>1043</v>
+      </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="47" t="s">
@@ -5066,8 +5508,8 @@
       <c r="J37" s="3" t="s">
         <v>972</v>
       </c>
-      <c r="K37" s="98" t="s">
-        <v>973</v>
+      <c r="K37" s="96" t="s">
+        <v>1044</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -5100,6 +5542,9 @@
       </c>
       <c r="J38" s="3" t="s">
         <v>57</v>
+      </c>
+      <c r="K38" s="97" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -5115,7 +5560,7 @@
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
+      <c r="K39" s="100"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="47" t="s">
@@ -5148,6 +5593,9 @@
       <c r="J40" s="8">
         <v>0</v>
       </c>
+      <c r="K40" s="97" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="47" t="s">
@@ -5180,6 +5628,9 @@
       <c r="J41" s="8">
         <v>0.05</v>
       </c>
+      <c r="K41" s="97" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="47" t="s">
@@ -5212,6 +5663,9 @@
       <c r="J42" s="8">
         <v>0.13</v>
       </c>
+      <c r="K42" s="105" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="47" t="s">
@@ -5244,6 +5698,9 @@
       <c r="J43" s="24">
         <v>0.05</v>
       </c>
+      <c r="K43" s="96" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="47" t="s">
@@ -5275,6 +5732,9 @@
       </c>
       <c r="J44" s="3" t="s">
         <v>57</v>
+      </c>
+      <c r="K44" s="97" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -5290,7 +5750,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
+      <c r="K45" s="100"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="47" t="s">
@@ -5323,6 +5783,9 @@
       <c r="J46" s="24">
         <v>0</v>
       </c>
+      <c r="K46" s="97" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="47" t="s">
@@ -5354,6 +5817,9 @@
       </c>
       <c r="J47" s="24">
         <v>0</v>
+      </c>
+      <c r="K47" s="97" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -5363,7 +5829,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A687902-E895-4B6B-A6CE-9EBEBC1827CF}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -5376,9 +5842,10 @@
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="65.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
         <v>394</v>
       </c>
@@ -5409,8 +5876,11 @@
       <c r="J1" s="50" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="50" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="49" t="s">
         <v>9</v>
       </c>
@@ -5423,8 +5893,9 @@
       <c r="H2" s="51"/>
       <c r="I2" s="51"/>
       <c r="J2" s="51"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="51"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>69</v>
       </c>
@@ -5437,8 +5908,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
         <v>10</v>
       </c>
@@ -5469,8 +5941,11 @@
       <c r="J4" s="8">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
         <v>11</v>
       </c>
@@ -5501,8 +5976,11 @@
       <c r="J5" s="8">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
         <v>116</v>
       </c>
@@ -5533,8 +6011,11 @@
       <c r="J6" s="8">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>70</v>
       </c>
@@ -5547,8 +6028,9 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="100"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
         <v>16</v>
       </c>
@@ -5576,9 +6058,14 @@
       <c r="I8" s="3">
         <v>24</v>
       </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="49" t="s">
         <v>17</v>
       </c>
@@ -5606,9 +6093,14 @@
       <c r="I9" s="3">
         <v>21</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K9" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="49" t="s">
         <v>18</v>
       </c>
@@ -5636,9 +6128,14 @@
       <c r="I10" s="3">
         <v>21</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K10" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="49" t="s">
         <v>19</v>
       </c>
@@ -5666,9 +6163,14 @@
       <c r="I11" s="3">
         <v>24</v>
       </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K11" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>24</v>
       </c>
@@ -5681,8 +6183,9 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="100"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="49" t="s">
         <v>25</v>
       </c>
@@ -5710,9 +6213,14 @@
       <c r="I13" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="49" t="s">
         <v>26</v>
       </c>
@@ -5740,9 +6248,14 @@
       <c r="I14" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K14" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="49" t="s">
         <v>27</v>
       </c>
@@ -5770,9 +6283,14 @@
       <c r="I15" s="3">
         <v>34</v>
       </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>68</v>
       </c>
@@ -5785,8 +6303,9 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="100"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="49" t="s">
         <v>396</v>
       </c>
@@ -5814,9 +6333,14 @@
       <c r="I17" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="K17" s="96" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="49" t="s">
         <v>397</v>
       </c>
@@ -5844,9 +6368,14 @@
       <c r="I18" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="K18" s="96" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="49" t="s">
         <v>398</v>
       </c>
@@ -5874,9 +6403,14 @@
       <c r="I19" s="3">
         <v>13</v>
       </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="K19" s="96" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="49" t="s">
         <v>395</v>
       </c>
@@ -5907,8 +6441,11 @@
       <c r="J20" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" s="103" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="49" t="s">
         <v>86</v>
       </c>
@@ -5936,8 +6473,14 @@
       <c r="I21" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J21" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="K21" s="96" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>67</v>
       </c>
@@ -5950,8 +6493,9 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K22" s="100"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="49" t="s">
         <v>42</v>
       </c>
@@ -5979,9 +6523,14 @@
       <c r="I23" s="3">
         <v>27</v>
       </c>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="K23" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="49" t="s">
         <v>43</v>
       </c>
@@ -6009,9 +6558,14 @@
       <c r="I24" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="K24" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="49" t="s">
         <v>44</v>
       </c>
@@ -6039,9 +6593,14 @@
       <c r="I25" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="49" t="s">
         <v>45</v>
       </c>
@@ -6069,9 +6628,14 @@
       <c r="I26" s="3">
         <v>29</v>
       </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K26" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="49" t="s">
         <v>46</v>
       </c>
@@ -6099,9 +6663,14 @@
       <c r="I27" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="J27" s="3"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K27" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>66</v>
       </c>
@@ -6114,8 +6683,9 @@
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="100"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="49" t="s">
         <v>52</v>
       </c>
@@ -6146,8 +6716,11 @@
       <c r="J29" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="49" t="s">
         <v>53</v>
       </c>
@@ -6178,8 +6751,11 @@
       <c r="J30" s="3" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="49" t="s">
         <v>54</v>
       </c>
@@ -6210,8 +6786,11 @@
       <c r="J31" s="3" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="97" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>71</v>
       </c>
@@ -6224,8 +6803,9 @@
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="100"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="49" t="s">
         <v>60</v>
       </c>
@@ -6256,8 +6836,11 @@
       <c r="J33" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="49" t="s">
         <v>61</v>
       </c>
@@ -6287,6 +6870,9 @@
       </c>
       <c r="J34" s="8">
         <v>0</v>
+      </c>
+      <c r="K34" s="102" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -6296,10 +6882,10 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B1DF3CB-5C1C-4C1F-BB79-231763A537BF}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
@@ -6309,9 +6895,10 @@
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="214.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="56" t="s">
         <v>423</v>
       </c>
@@ -6342,8 +6929,11 @@
       <c r="J1" s="42" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="42" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
         <v>9</v>
       </c>
@@ -6356,8 +6946,9 @@
       <c r="H2" s="43"/>
       <c r="I2" s="43"/>
       <c r="J2" s="43"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="43"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>69</v>
       </c>
@@ -6370,8 +6961,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="56" t="s">
         <v>10</v>
       </c>
@@ -6402,8 +6994,11 @@
       <c r="J4" s="8">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="56" t="s">
         <v>11</v>
       </c>
@@ -6434,8 +7029,11 @@
       <c r="J5" s="8">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="56" t="s">
         <v>116</v>
       </c>
@@ -6466,8 +7064,11 @@
       <c r="J6" s="8">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>70</v>
       </c>
@@ -6480,8 +7081,9 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="100"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="56" t="s">
         <v>16</v>
       </c>
@@ -6509,9 +7111,14 @@
       <c r="I8" s="3">
         <v>21</v>
       </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K8" s="96" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="56" t="s">
         <v>17</v>
       </c>
@@ -6539,9 +7146,14 @@
       <c r="I9" s="3">
         <v>24</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="96" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="56" t="s">
         <v>18</v>
       </c>
@@ -6569,9 +7181,14 @@
       <c r="I10" s="3">
         <v>29</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K10" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="56" t="s">
         <v>19</v>
       </c>
@@ -6599,9 +7216,14 @@
       <c r="I11" s="3">
         <v>30</v>
       </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>24</v>
       </c>
@@ -6614,8 +7236,9 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="100"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="56" t="s">
         <v>25</v>
       </c>
@@ -6643,9 +7266,14 @@
       <c r="I13" s="3">
         <v>27</v>
       </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="56" t="s">
         <v>26</v>
       </c>
@@ -6673,9 +7301,14 @@
       <c r="I14" s="3">
         <v>35</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K14" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="56" t="s">
         <v>27</v>
       </c>
@@ -6703,9 +7336,14 @@
       <c r="I15" s="3">
         <v>37</v>
       </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="K15" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>68</v>
       </c>
@@ -6718,8 +7356,9 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="100"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="56" t="s">
         <v>426</v>
       </c>
@@ -6750,8 +7389,11 @@
       <c r="J17" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="103" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="56" t="s">
         <v>427</v>
       </c>
@@ -6782,8 +7424,11 @@
       <c r="J18" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K18" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="56" t="s">
         <v>740</v>
       </c>
@@ -6802,8 +7447,8 @@
       <c r="F19" s="3">
         <v>0</v>
       </c>
-      <c r="G19" s="3">
-        <v>50</v>
+      <c r="G19" s="3" t="s">
+        <v>1053</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>442</v>
@@ -6811,9 +7456,14 @@
       <c r="I19" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="K19" s="96" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="56" t="s">
         <v>428</v>
       </c>
@@ -6844,54 +7494,61 @@
       <c r="J20" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="K20" s="103"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="56" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B21" s="3">
+        <v>10</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>1062</v>
+      </c>
+      <c r="K21" s="103" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="56" t="s">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="100"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="56" t="s">
         <v>430</v>
-      </c>
-      <c r="B22" s="3">
-        <v>10</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>491</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>6</v>
-      </c>
-      <c r="I22" s="3">
-        <v>9</v>
-      </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="56" t="s">
-        <v>431</v>
       </c>
       <c r="B23" s="3">
         <v>10</v>
@@ -6917,11 +7574,16 @@
       <c r="I23" s="3">
         <v>9</v>
       </c>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="K23" s="96" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="56" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B24" s="3">
         <v>10</v>
@@ -6936,165 +7598,191 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>491</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>6</v>
+      </c>
+      <c r="I24" s="3">
+        <v>9</v>
+      </c>
+      <c r="J24" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="K24" s="96" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="56" t="s">
+        <v>432</v>
+      </c>
+      <c r="B25" s="3">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
         <v>231</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
         <v>11</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I25" s="3">
         <v>34</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="J25" s="8">
+        <v>0.18</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="56" t="s">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="100"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B27" s="3">
         <v>6</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D27" s="3">
         <v>9</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E27" s="3">
         <v>-16</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F27" s="3">
         <v>49</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H27" s="3">
         <v>9</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I27" s="3">
         <v>27</v>
       </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="56" t="s">
+      <c r="J27" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="K27" s="96" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B28" s="3">
         <v>11</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D28" s="3">
         <v>35</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E28" s="3">
         <v>-20</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F28" s="3">
         <v>69</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I28" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="J27" s="3"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="56" t="s">
+      <c r="J28" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="K28" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B29" s="3">
         <v>9</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D29" s="3">
         <v>19</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E29" s="3">
         <v>-11</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F29" s="3">
         <v>49</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="H28" s="3">
-        <v>10</v>
-      </c>
-      <c r="I28" s="3">
-        <v>29</v>
-      </c>
-      <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="56" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="3">
-        <v>10</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="D29" s="3">
-        <v>24</v>
-      </c>
-      <c r="E29" s="3">
-        <v>1</v>
-      </c>
-      <c r="F29" s="3">
-        <v>39</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="H29" s="3">
         <v>10</v>
       </c>
       <c r="I29" s="3">
-        <v>30</v>
-      </c>
-      <c r="J29" s="3"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="K29" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B30" s="3">
         <v>10</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>218</v>
+        <v>450</v>
       </c>
       <c r="D30" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E30" s="3">
         <v>1</v>
@@ -7103,7 +7791,7 @@
         <v>39</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>474</v>
+        <v>354</v>
       </c>
       <c r="H30" s="3">
         <v>10</v>
@@ -7111,167 +7799,186 @@
       <c r="I30" s="3">
         <v>30</v>
       </c>
-      <c r="J30" s="3"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
+      <c r="J30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K30" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="3">
+        <v>10</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D31" s="3">
+        <v>13</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3">
+        <v>39</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="H31" s="3">
+        <v>10</v>
+      </c>
+      <c r="I31" s="3">
+        <v>30</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="K31" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="56" t="s">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="100"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B33" s="3">
         <v>6</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C33" s="3">
         <v>6</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D33" s="3">
         <v>15</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>34</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="56" t="s">
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0</v>
+      </c>
+      <c r="K33" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B34" s="3">
         <v>4</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D34" s="3">
         <v>37</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3">
         <v>59</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="s">
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="56" t="s">
+      <c r="K34" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B35" s="3">
         <v>3</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D35" s="3">
         <v>38</v>
       </c>
-      <c r="E34" s="3">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3">
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>54</v>
       </c>
-      <c r="G34" s="3">
-        <v>0</v>
-      </c>
-      <c r="H34" s="3">
-        <v>0</v>
-      </c>
-      <c r="I34" s="3">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="s">
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
+      <c r="K35" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="56" t="s">
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="100"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="56" t="s">
         <v>60</v>
-      </c>
-      <c r="B36" s="3">
-        <v>4</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" s="3">
-        <v>15</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3">
-        <v>34</v>
-      </c>
-      <c r="G36" s="3">
-        <v>0</v>
-      </c>
-      <c r="H36" s="3">
-        <v>0</v>
-      </c>
-      <c r="I36" s="3">
-        <v>0</v>
-      </c>
-      <c r="J36" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="56" t="s">
-        <v>61</v>
       </c>
       <c r="B37" s="3">
         <v>4</v>
@@ -7299,6 +8006,44 @@
       </c>
       <c r="J37" s="8">
         <v>0</v>
+      </c>
+      <c r="K37" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="3">
+        <v>4</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" s="3">
+        <v>15</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3">
+        <v>34</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="8">
+        <v>0</v>
+      </c>
+      <c r="K38" s="102" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -7308,7 +8053,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D71A7D61-0009-472F-855B-FD4BD2F72D00}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -7321,9 +8066,10 @@
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="109.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>424</v>
       </c>
@@ -7354,8 +8100,11 @@
       <c r="J1" s="19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="19" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
@@ -7368,8 +8117,9 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
       <c r="J2" s="20"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>69</v>
       </c>
@@ -7382,8 +8132,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>10</v>
       </c>
@@ -7414,8 +8165,11 @@
       <c r="J4" s="8">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>11</v>
       </c>
@@ -7446,8 +8200,11 @@
       <c r="J5" s="8">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>116</v>
       </c>
@@ -7478,8 +8235,11 @@
       <c r="J6" s="8">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>182</v>
       </c>
@@ -7510,8 +8270,11 @@
       <c r="J7" s="8">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="102" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>70</v>
       </c>
@@ -7524,8 +8287,9 @@
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="100"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>16</v>
       </c>
@@ -7553,9 +8317,14 @@
       <c r="I9" s="3">
         <v>22</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="K9" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>17</v>
       </c>
@@ -7583,9 +8352,14 @@
       <c r="I10" s="3">
         <v>17</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K10" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>18</v>
       </c>
@@ -7613,9 +8387,14 @@
       <c r="I11" s="3">
         <v>30</v>
       </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="K11" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>19</v>
       </c>
@@ -7643,9 +8422,14 @@
       <c r="I12" s="3">
         <v>21</v>
       </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K12" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
@@ -7658,8 +8442,9 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" s="100"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -7687,9 +8472,14 @@
       <c r="I14" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="K14" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -7717,9 +8507,14 @@
       <c r="I15" s="3">
         <v>34</v>
       </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>27</v>
       </c>
@@ -7747,9 +8542,14 @@
       <c r="I16" s="3">
         <v>34</v>
       </c>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K16" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>68</v>
       </c>
@@ -7762,8 +8562,9 @@
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="100"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>738</v>
       </c>
@@ -7791,9 +8592,14 @@
       <c r="I18" s="3">
         <v>14</v>
       </c>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="K18" s="103" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>40</v>
       </c>
@@ -7821,9 +8627,14 @@
       <c r="I19" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="K19" s="96" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>117</v>
       </c>
@@ -7851,9 +8662,14 @@
       <c r="I20" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="K20" s="96" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>141</v>
       </c>
@@ -7881,11 +8697,14 @@
       <c r="I21" s="3">
         <v>14</v>
       </c>
-      <c r="J21" s="24">
+      <c r="J21" s="8">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" s="103" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>739</v>
       </c>
@@ -7901,7 +8720,7 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="3" t="s">
         <v>262</v>
       </c>
       <c r="G22" s="3">
@@ -7913,11 +8732,14 @@
       <c r="I22" s="3">
         <v>16</v>
       </c>
-      <c r="J22" s="24">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K22" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>67</v>
       </c>
@@ -7930,8 +8752,9 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23" s="100"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>42</v>
       </c>
@@ -7959,9 +8782,14 @@
       <c r="I24" s="3">
         <v>26</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K24" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>43</v>
       </c>
@@ -7989,9 +8817,14 @@
       <c r="I25" s="3">
         <v>29</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>44</v>
       </c>
@@ -8019,9 +8852,14 @@
       <c r="I26" s="3">
         <v>30</v>
       </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K26" s="96" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>45</v>
       </c>
@@ -8049,9 +8887,14 @@
       <c r="I27" s="3">
         <v>34</v>
       </c>
-      <c r="J27" s="3"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="K27" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>46</v>
       </c>
@@ -8079,9 +8922,14 @@
       <c r="I28" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="K28" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>66</v>
       </c>
@@ -8094,8 +8942,9 @@
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="100"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>52</v>
       </c>
@@ -8126,8 +8975,11 @@
       <c r="J30" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="103" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>53</v>
       </c>
@@ -8158,8 +9010,11 @@
       <c r="J31" s="8" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>54</v>
       </c>
@@ -8190,8 +9045,11 @@
       <c r="J32" s="8" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>71</v>
       </c>
@@ -8204,8 +9062,9 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="100"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>60</v>
       </c>
@@ -8234,10 +9093,13 @@
         <v>0</v>
       </c>
       <c r="J34" s="8">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="K34" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>61</v>
       </c>
@@ -8267,6 +9129,9 @@
       </c>
       <c r="J35" s="8">
         <v>0</v>
+      </c>
+      <c r="K35" s="102" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -8277,7 +9142,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DE3DAA9-1C71-4D0E-8B48-1B27293C1673}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
@@ -8285,9 +9150,10 @@
     <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="81.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
         <v>205</v>
       </c>
@@ -8318,8 +9184,11 @@
       <c r="J1" s="28" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="28" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>9</v>
       </c>
@@ -8332,8 +9201,9 @@
       <c r="H2" s="29"/>
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="29"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>69</v>
       </c>
@@ -8346,8 +9216,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>10</v>
       </c>
@@ -8378,8 +9249,11 @@
       <c r="J4" s="8">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>11</v>
       </c>
@@ -8410,8 +9284,11 @@
       <c r="J5" s="24">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>116</v>
       </c>
@@ -8442,8 +9319,11 @@
       <c r="J6" s="24">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>70</v>
       </c>
@@ -8456,8 +9336,9 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="100"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
         <v>16</v>
       </c>
@@ -8485,9 +9366,14 @@
       <c r="I8" s="3">
         <v>9</v>
       </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="K8" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>17</v>
       </c>
@@ -8515,9 +9401,14 @@
       <c r="I9" s="3">
         <v>16</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="K9" s="96" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
         <v>18</v>
       </c>
@@ -8545,9 +9436,14 @@
       <c r="I10" s="3">
         <v>21</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K10" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
         <v>19</v>
       </c>
@@ -8575,9 +9471,14 @@
       <c r="I11" s="3">
         <v>24</v>
       </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="K11" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>24</v>
       </c>
@@ -8590,8 +9491,9 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="100"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
         <v>25</v>
       </c>
@@ -8619,9 +9521,14 @@
       <c r="I13" s="3">
         <v>35</v>
       </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="K13" s="96" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
         <v>26</v>
       </c>
@@ -8649,9 +9556,14 @@
       <c r="I14" s="3">
         <v>32</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="K14" s="96" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
         <v>27</v>
       </c>
@@ -8679,9 +9591,14 @@
       <c r="I15" s="3">
         <v>34</v>
       </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="96" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>68</v>
       </c>
@@ -8694,8 +9611,9 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="100"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
         <v>84</v>
       </c>
@@ -8726,8 +9644,11 @@
       <c r="J17" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="104" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
         <v>776</v>
       </c>
@@ -8755,9 +9676,14 @@
       <c r="I18" s="3">
         <v>14</v>
       </c>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="8" t="s">
+        <v>864</v>
+      </c>
+      <c r="K18" s="103" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
         <v>741</v>
       </c>
@@ -8785,9 +9711,14 @@
       <c r="I19" s="3">
         <v>53</v>
       </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K19" s="96" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="33" t="s">
         <v>742</v>
       </c>
@@ -8815,9 +9746,14 @@
       <c r="I20" s="3">
         <v>53</v>
       </c>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K20" s="96" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="33" t="s">
         <v>183</v>
       </c>
@@ -8845,9 +9781,14 @@
       <c r="I21" s="3">
         <v>11</v>
       </c>
-      <c r="J21" s="24"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J21" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="K21" s="103" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
         <v>184</v>
       </c>
@@ -8875,8 +9816,14 @@
       <c r="I22" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="K22" s="103" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>67</v>
       </c>
@@ -8889,8 +9836,9 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23" s="100"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
         <v>42</v>
       </c>
@@ -8918,9 +9866,14 @@
       <c r="I24" s="3">
         <v>27</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="K24" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="33" t="s">
         <v>43</v>
       </c>
@@ -8948,9 +9901,14 @@
       <c r="I25" s="3">
         <v>29</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="33" t="s">
         <v>44</v>
       </c>
@@ -8978,9 +9936,14 @@
       <c r="I26" s="3">
         <v>29</v>
       </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K26" s="96" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="33" t="s">
         <v>45</v>
       </c>
@@ -9008,9 +9971,14 @@
       <c r="I27" s="3">
         <v>24</v>
       </c>
-      <c r="J27" s="3"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="K27" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
         <v>46</v>
       </c>
@@ -9038,9 +10006,14 @@
       <c r="I28" s="3">
         <v>30</v>
       </c>
-      <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="K28" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>66</v>
       </c>
@@ -9053,8 +10026,9 @@
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="100"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="33" t="s">
         <v>52</v>
       </c>
@@ -9085,8 +10059,11 @@
       <c r="J30" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="33" t="s">
         <v>53</v>
       </c>
@@ -9117,8 +10094,11 @@
       <c r="J31" s="8" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="33" t="s">
         <v>54</v>
       </c>
@@ -9149,8 +10129,11 @@
       <c r="J32" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>71</v>
       </c>
@@ -9163,8 +10146,9 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="100"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="33" t="s">
         <v>60</v>
       </c>
@@ -9195,8 +10179,11 @@
       <c r="J34" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K34" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="33" t="s">
         <v>61</v>
       </c>
@@ -9227,6 +10214,12 @@
       <c r="J35" s="24">
         <v>0</v>
       </c>
+      <c r="K35" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K36" s="96"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9235,7 +10228,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364C5920-1C33-40BA-9652-8F894AA3F125}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
@@ -9243,9 +10236,10 @@
     <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="68.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
         <v>219</v>
       </c>
@@ -9276,8 +10270,11 @@
       <c r="J1" s="19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="19" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>9</v>
       </c>
@@ -9290,8 +10287,9 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
       <c r="J2" s="20"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>69</v>
       </c>
@@ -9304,8 +10302,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
         <v>10</v>
       </c>
@@ -9336,8 +10335,11 @@
       <c r="J4" s="8">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>11</v>
       </c>
@@ -9368,8 +10370,11 @@
       <c r="J5" s="24">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>70</v>
       </c>
@@ -9382,8 +10387,9 @@
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="100"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>16</v>
       </c>
@@ -9411,9 +10417,14 @@
       <c r="I7" s="3">
         <v>21</v>
       </c>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K7" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>17</v>
       </c>
@@ -9441,9 +10452,14 @@
       <c r="I8" s="3">
         <v>24</v>
       </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="96" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>18</v>
       </c>
@@ -9471,9 +10487,14 @@
       <c r="I9" s="3">
         <v>26</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="K9" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
         <v>19</v>
       </c>
@@ -9501,9 +10522,14 @@
       <c r="I10" s="3">
         <v>24</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K10" s="96" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>24</v>
       </c>
@@ -9516,8 +10542,9 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="100"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
         <v>25</v>
       </c>
@@ -9545,9 +10572,14 @@
       <c r="I12" s="3">
         <v>27</v>
       </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="K12" s="106" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>26</v>
       </c>
@@ -9575,9 +10607,14 @@
       <c r="I13" s="3">
         <v>34</v>
       </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K13" s="96" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
         <v>27</v>
       </c>
@@ -9605,9 +10642,14 @@
       <c r="I14" s="3">
         <v>34</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K14" s="96" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>68</v>
       </c>
@@ -9620,8 +10662,9 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="100"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
         <v>242</v>
       </c>
@@ -9637,8 +10680,8 @@
       <c r="E16" s="3">
         <v>-18</v>
       </c>
-      <c r="F16" s="3">
-        <v>82</v>
+      <c r="F16" s="3" t="s">
+        <v>1097</v>
       </c>
       <c r="G16" s="3">
         <v>44</v>
@@ -9649,9 +10692,14 @@
       <c r="I16" s="3">
         <v>34</v>
       </c>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K16" s="103" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>246</v>
       </c>
@@ -9679,8 +10727,14 @@
       <c r="I17" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="K17" s="96" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
         <v>83</v>
       </c>
@@ -9708,9 +10762,14 @@
       <c r="I18" s="3">
         <v>27</v>
       </c>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="K18" s="103" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>240</v>
       </c>
@@ -9741,8 +10800,11 @@
       <c r="J19" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K19" s="103" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
         <v>241</v>
       </c>
@@ -9770,9 +10832,14 @@
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="24"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="8" t="s">
+        <v>1016</v>
+      </c>
+      <c r="K20" s="103" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>67</v>
       </c>
@@ -9785,8 +10852,9 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" s="100"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
         <v>42</v>
       </c>
@@ -9814,9 +10882,14 @@
       <c r="I22" s="3">
         <v>27</v>
       </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="K22" s="107" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>43</v>
       </c>
@@ -9844,9 +10917,14 @@
       <c r="I23" s="3">
         <v>29</v>
       </c>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K23" s="107" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="34" t="s">
         <v>44</v>
       </c>
@@ -9874,9 +10952,14 @@
       <c r="I24" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="K24" s="107" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
         <v>45</v>
       </c>
@@ -9904,9 +10987,14 @@
       <c r="I25" s="3">
         <v>34</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K25" s="107" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
         <v>46</v>
       </c>
@@ -9934,9 +11022,14 @@
       <c r="I26" s="3">
         <v>30</v>
       </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K26" s="107" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>66</v>
       </c>
@@ -9949,8 +11042,9 @@
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" s="100"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="34" t="s">
         <v>52</v>
       </c>
@@ -9981,8 +11075,11 @@
       <c r="J28" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="34" t="s">
         <v>53</v>
       </c>
@@ -10013,8 +11110,11 @@
       <c r="J29" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="34" t="s">
         <v>54</v>
       </c>
@@ -10045,8 +11145,11 @@
       <c r="J30" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>71</v>
       </c>
@@ -10059,8 +11162,9 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="100"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
         <v>60</v>
       </c>
@@ -10091,8 +11195,11 @@
       <c r="J32" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
         <v>61</v>
       </c>
@@ -10123,8 +11230,11 @@
       <c r="J33" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -10703,7 +11813,7 @@
         <v>42</v>
       </c>
       <c r="B22" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>270</v>
@@ -14557,7 +15667,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{251D0984-0D2F-477E-9F16-06AA991EC964}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -14570,9 +15680,10 @@
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="47.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
         <v>376</v>
       </c>
@@ -14603,8 +15714,11 @@
       <c r="J1" s="45" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="45" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="s">
         <v>9</v>
       </c>
@@ -14617,8 +15731,9 @@
       <c r="H2" s="46"/>
       <c r="I2" s="46"/>
       <c r="J2" s="46"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="46"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>69</v>
       </c>
@@ -14631,8 +15746,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="44" t="s">
         <v>10</v>
       </c>
@@ -14663,8 +15779,11 @@
       <c r="J4" s="8">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
         <v>11</v>
       </c>
@@ -14695,8 +15814,11 @@
       <c r="J5" s="8">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="44" t="s">
         <v>116</v>
       </c>
@@ -14727,8 +15849,11 @@
       <c r="J6" s="8">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>70</v>
       </c>
@@ -14741,8 +15866,9 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="100"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="44" t="s">
         <v>16</v>
       </c>
@@ -14770,9 +15896,14 @@
       <c r="I8" s="3">
         <v>26</v>
       </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="K8" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="44" t="s">
         <v>17</v>
       </c>
@@ -14800,9 +15931,14 @@
       <c r="I9" s="3">
         <v>22</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="K9" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
         <v>18</v>
       </c>
@@ -14830,9 +15966,14 @@
       <c r="I10" s="3">
         <v>24</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
         <v>19</v>
       </c>
@@ -14860,9 +16001,14 @@
       <c r="I11" s="3">
         <v>24</v>
       </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
@@ -14875,8 +16021,9 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="100"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
         <v>25</v>
       </c>
@@ -14904,9 +16051,14 @@
       <c r="I13" s="3">
         <v>35</v>
       </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="K13" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
         <v>26</v>
       </c>
@@ -14934,9 +16086,14 @@
       <c r="I14" s="3">
         <v>37</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="K14" s="96" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
         <v>27</v>
       </c>
@@ -14964,9 +16121,14 @@
       <c r="I15" s="3">
         <v>34</v>
       </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="96" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>68</v>
       </c>
@@ -14979,8 +16141,9 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="100"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="44" t="s">
         <v>35</v>
       </c>
@@ -15008,9 +16171,14 @@
       <c r="I17" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="K17" s="96" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
         <v>36</v>
       </c>
@@ -15038,9 +16206,14 @@
       <c r="I18" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="K18" s="96" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="s">
         <v>40</v>
       </c>
@@ -15068,9 +16241,14 @@
       <c r="I19" s="3">
         <v>30</v>
       </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="K19" s="96" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="44" t="s">
         <v>31</v>
       </c>
@@ -15098,9 +16276,14 @@
       <c r="I20" s="3">
         <v>19</v>
       </c>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K20" s="96" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>67</v>
       </c>
@@ -15113,8 +16296,9 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" s="100"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="44" t="s">
         <v>42</v>
       </c>
@@ -15142,9 +16326,14 @@
       <c r="I22" s="3">
         <v>22</v>
       </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="K22" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="44" t="s">
         <v>43</v>
       </c>
@@ -15172,9 +16361,14 @@
       <c r="I23" s="3">
         <v>24</v>
       </c>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="K23" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="44" t="s">
         <v>44</v>
       </c>
@@ -15202,9 +16396,14 @@
       <c r="I24" s="3">
         <v>27</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="K24" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="44" t="s">
         <v>45</v>
       </c>
@@ -15232,9 +16431,14 @@
       <c r="I25" s="3">
         <v>32</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="44" t="s">
         <v>46</v>
       </c>
@@ -15262,9 +16466,14 @@
       <c r="I26" s="3">
         <v>27</v>
       </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="K26" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>66</v>
       </c>
@@ -15277,8 +16486,9 @@
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" s="100"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="44" t="s">
         <v>52</v>
       </c>
@@ -15309,8 +16519,11 @@
       <c r="J28" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="44" t="s">
         <v>53</v>
       </c>
@@ -15341,8 +16554,11 @@
       <c r="J29" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="44" t="s">
         <v>54</v>
       </c>
@@ -15373,8 +16589,11 @@
       <c r="J30" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>71</v>
       </c>
@@ -15387,8 +16606,9 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="100"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="44" t="s">
         <v>60</v>
       </c>
@@ -15419,8 +16639,11 @@
       <c r="J32" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="44" t="s">
         <v>61</v>
       </c>
@@ -15450,6 +16673,9 @@
       </c>
       <c r="J33" s="8">
         <v>0</v>
+      </c>
+      <c r="K33" s="97" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -24648,7 +25874,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A2E699-42B9-4884-9E37-FDB4475CABD3}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -24661,9 +25887,10 @@
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="69.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -24694,8 +25921,11 @@
       <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -24708,8 +25938,9 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="7"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>69</v>
       </c>
@@ -24722,8 +25953,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -24754,8 +25986,11 @@
       <c r="J4" s="8">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -24786,8 +26021,11 @@
       <c r="J5" s="8">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>116</v>
       </c>
@@ -24818,8 +26056,11 @@
       <c r="J6" s="8">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>70</v>
       </c>
@@ -24832,8 +26073,9 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="100"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
@@ -24861,9 +26103,14 @@
       <c r="I8" s="3">
         <v>16</v>
       </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="K8" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -24891,9 +26138,14 @@
       <c r="I9" s="3">
         <v>21</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K9" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -24921,9 +26173,14 @@
       <c r="I10" s="3">
         <v>21</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K10" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
@@ -24951,9 +26208,14 @@
       <c r="I11" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="K11" s="96" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
@@ -24966,8 +26228,9 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="100"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>25</v>
       </c>
@@ -24995,9 +26258,14 @@
       <c r="I13" s="3">
         <v>32</v>
       </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="K13" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
@@ -25025,9 +26293,14 @@
       <c r="I14" s="3">
         <v>35</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="K14" s="96" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
@@ -25055,9 +26328,14 @@
       <c r="I15" s="3">
         <v>29</v>
       </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K15" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>68</v>
       </c>
@@ -25070,8 +26348,9 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="100"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>35</v>
       </c>
@@ -25099,9 +26378,14 @@
       <c r="I17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="K17" s="96" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>36</v>
       </c>
@@ -25129,9 +26413,14 @@
       <c r="I18" s="3">
         <v>29</v>
       </c>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K18" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>83</v>
       </c>
@@ -25162,8 +26451,11 @@
       <c r="J19" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K19" s="96" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -25191,9 +26483,14 @@
       <c r="I20" s="3">
         <v>14</v>
       </c>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="K20" s="96" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>67</v>
       </c>
@@ -25206,8 +26503,9 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" s="100"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>42</v>
       </c>
@@ -25235,9 +26533,14 @@
       <c r="I22" s="3">
         <v>27</v>
       </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="K22" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>43</v>
       </c>
@@ -25265,9 +26568,14 @@
       <c r="I23" s="3">
         <v>24</v>
       </c>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K23" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>44</v>
       </c>
@@ -25295,9 +26603,14 @@
       <c r="I24" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="K24" s="96" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>45</v>
       </c>
@@ -25325,9 +26638,14 @@
       <c r="I25" s="3">
         <v>30</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>46</v>
       </c>
@@ -25355,9 +26673,14 @@
       <c r="I26" s="3">
         <v>30</v>
       </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="K26" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>66</v>
       </c>
@@ -25370,8 +26693,9 @@
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" s="100"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>52</v>
       </c>
@@ -25402,8 +26726,11 @@
       <c r="J28" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>53</v>
       </c>
@@ -25434,8 +26761,11 @@
       <c r="J29" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>54</v>
       </c>
@@ -25466,8 +26796,11 @@
       <c r="J30" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>71</v>
       </c>
@@ -25480,8 +26813,9 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="100"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>60</v>
       </c>
@@ -25512,8 +26846,11 @@
       <c r="J32" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>61</v>
       </c>
@@ -25544,8 +26881,11 @@
       <c r="J33" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>63</v>
       </c>
@@ -25576,8 +26916,11 @@
       <c r="J34" s="8">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K34" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -25588,7 +26931,7 @@
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -25599,7 +26942,7 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -34790,7 +36133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD78D5A-CE64-4C1F-97DA-696E4F24DB02}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -34802,9 +36145,10 @@
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="14" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="47.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>65</v>
       </c>
@@ -34835,8 +36179,11 @@
       <c r="J1" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="11" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>9</v>
       </c>
@@ -34849,8 +36196,9 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>69</v>
       </c>
@@ -34863,8 +36211,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
@@ -34895,8 +36244,11 @@
       <c r="J4" s="8">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
@@ -34927,8 +36279,11 @@
       <c r="J5" s="8">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>116</v>
       </c>
@@ -34959,8 +36314,11 @@
       <c r="J6" s="8">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>70</v>
       </c>
@@ -34973,8 +36331,9 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="100"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>16</v>
       </c>
@@ -35002,9 +36361,14 @@
       <c r="I8" s="3">
         <v>24</v>
       </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>17</v>
       </c>
@@ -35032,9 +36396,14 @@
       <c r="I9" s="3">
         <v>21</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K9" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
@@ -35062,9 +36431,14 @@
       <c r="I10" s="3">
         <v>26</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="K10" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>19</v>
       </c>
@@ -35092,9 +36466,14 @@
       <c r="I11" s="3">
         <v>24</v>
       </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="K11" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>24</v>
       </c>
@@ -35107,8 +36486,9 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="100"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>25</v>
       </c>
@@ -35136,9 +36516,14 @@
       <c r="I13" s="3">
         <v>32</v>
       </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="K13" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>26</v>
       </c>
@@ -35166,9 +36551,14 @@
       <c r="I14" s="3">
         <v>35</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="K14" s="96" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>27</v>
       </c>
@@ -35196,9 +36586,14 @@
       <c r="I15" s="3">
         <v>32</v>
       </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="K15" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>68</v>
       </c>
@@ -35211,8 +36606,9 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="100"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>35</v>
       </c>
@@ -35240,9 +36636,14 @@
       <c r="I17" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="K17" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>36</v>
       </c>
@@ -35270,9 +36671,14 @@
       <c r="I18" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="K18" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>83</v>
       </c>
@@ -35301,10 +36707,13 @@
         <v>734</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>996</v>
+      </c>
+      <c r="K19" s="96" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>31</v>
       </c>
@@ -35332,9 +36741,14 @@
       <c r="I20" s="3">
         <v>16</v>
       </c>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="K20" s="96" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>67</v>
       </c>
@@ -35347,8 +36761,9 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" s="100"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>42</v>
       </c>
@@ -35376,9 +36791,14 @@
       <c r="I22" s="3">
         <v>27</v>
       </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="K22" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>43</v>
       </c>
@@ -35406,9 +36826,14 @@
       <c r="I23" s="3">
         <v>24</v>
       </c>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="K23" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>44</v>
       </c>
@@ -35436,9 +36861,14 @@
       <c r="I24" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="K24" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>45</v>
       </c>
@@ -35466,9 +36896,14 @@
       <c r="I25" s="3">
         <v>30</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>46</v>
       </c>
@@ -35496,9 +36931,14 @@
       <c r="I26" s="3">
         <v>30</v>
       </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="K26" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>66</v>
       </c>
@@ -35511,8 +36951,9 @@
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" s="100"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>52</v>
       </c>
@@ -35543,8 +36984,11 @@
       <c r="J28" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>53</v>
       </c>
@@ -35575,8 +37019,11 @@
       <c r="J29" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>54</v>
       </c>
@@ -35607,8 +37054,11 @@
       <c r="J30" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>71</v>
       </c>
@@ -35621,8 +37071,9 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="100"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>60</v>
       </c>
@@ -35653,8 +37104,11 @@
       <c r="J32" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>61</v>
       </c>
@@ -35685,8 +37139,11 @@
       <c r="J33" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -41058,7 +42515,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5423C4A2-3E21-4DF4-9BD6-D2F670510E5E}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -41071,9 +42528,10 @@
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="42.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>82</v>
       </c>
@@ -41104,8 +42562,11 @@
       <c r="J1" s="15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="15" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>9</v>
       </c>
@@ -41118,8 +42579,9 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="16"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="16"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>69</v>
       </c>
@@ -41132,8 +42594,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>10</v>
       </c>
@@ -41164,8 +42627,11 @@
       <c r="J4" s="8">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>11</v>
       </c>
@@ -41196,8 +42662,11 @@
       <c r="J5" s="8">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>70</v>
       </c>
@@ -41210,8 +42679,9 @@
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="100"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>16</v>
       </c>
@@ -41239,9 +42709,14 @@
       <c r="I7" s="3">
         <v>17</v>
       </c>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>17</v>
       </c>
@@ -41269,9 +42744,14 @@
       <c r="I8" s="3">
         <v>26</v>
       </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="K8" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>18</v>
       </c>
@@ -41299,9 +42779,14 @@
       <c r="I9" s="3">
         <v>24</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>19</v>
       </c>
@@ -41329,9 +42814,14 @@
       <c r="I10" s="3">
         <v>24</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>24</v>
       </c>
@@ -41344,8 +42834,9 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="100"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>25</v>
       </c>
@@ -41373,9 +42864,14 @@
       <c r="I12" s="3">
         <v>35</v>
       </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="K12" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>26</v>
       </c>
@@ -41403,9 +42899,14 @@
       <c r="I13" s="3">
         <v>39</v>
       </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="K13" s="96" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>27</v>
       </c>
@@ -41433,9 +42934,14 @@
       <c r="I14" s="3">
         <v>37</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="K14" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>68</v>
       </c>
@@ -41448,8 +42954,9 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="100"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>85</v>
       </c>
@@ -41480,8 +42987,11 @@
       <c r="J16" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="103" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>86</v>
       </c>
@@ -41512,8 +43022,11 @@
       <c r="J17" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="96" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>83</v>
       </c>
@@ -41541,9 +43054,14 @@
       <c r="I18" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="K18" s="96" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>84</v>
       </c>
@@ -41571,9 +43089,14 @@
       <c r="I19" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K19" s="96" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>67</v>
       </c>
@@ -41586,8 +43109,9 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" s="100"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>42</v>
       </c>
@@ -41615,9 +43139,14 @@
       <c r="I21" s="3">
         <v>29</v>
       </c>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J21" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="K21" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>43</v>
       </c>
@@ -41645,9 +43174,14 @@
       <c r="I22" s="3">
         <v>24</v>
       </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>44</v>
       </c>
@@ -41675,9 +43209,14 @@
       <c r="I23" s="3">
         <v>26</v>
       </c>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="K23" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>45</v>
       </c>
@@ -41705,9 +43244,14 @@
       <c r="I24" s="3">
         <v>30</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K24" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>46</v>
       </c>
@@ -41735,9 +43279,14 @@
       <c r="I25" s="3">
         <v>29</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>66</v>
       </c>
@@ -41750,8 +43299,9 @@
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K26" s="100"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>52</v>
       </c>
@@ -41782,8 +43332,11 @@
       <c r="J27" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>87</v>
       </c>
@@ -41814,8 +43367,11 @@
       <c r="J28" s="8">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>53</v>
       </c>
@@ -41846,8 +43402,11 @@
       <c r="J29" s="3" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>54</v>
       </c>
@@ -41878,8 +43437,11 @@
       <c r="J30" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>71</v>
       </c>
@@ -41892,8 +43454,9 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="100"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>60</v>
       </c>
@@ -41924,8 +43487,11 @@
       <c r="J32" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>61</v>
       </c>
@@ -41956,11 +43522,15 @@
       <c r="J33" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="96" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K34" s="96"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
     </row>
   </sheetData>
@@ -41970,7 +43540,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22BFB010-DFD6-4AC8-82BA-CAF94D7A1964}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -41983,9 +43553,10 @@
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="87.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>115</v>
       </c>
@@ -42016,8 +43587,11 @@
       <c r="J1" s="19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="19" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
@@ -42030,8 +43604,9 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
       <c r="J2" s="20"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>69</v>
       </c>
@@ -42044,8 +43619,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>10</v>
       </c>
@@ -42076,8 +43652,11 @@
       <c r="J4" s="8">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>11</v>
       </c>
@@ -42108,8 +43687,11 @@
       <c r="J5" s="8">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>116</v>
       </c>
@@ -42140,8 +43722,11 @@
       <c r="J6" s="8">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>182</v>
       </c>
@@ -42172,8 +43757,11 @@
       <c r="J7" s="8">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>70</v>
       </c>
@@ -42186,8 +43774,9 @@
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="100"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>16</v>
       </c>
@@ -42215,9 +43804,14 @@
       <c r="I9" s="3">
         <v>24</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>17</v>
       </c>
@@ -42245,9 +43839,14 @@
       <c r="I10" s="3">
         <v>21</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K10" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>18</v>
       </c>
@@ -42275,9 +43874,14 @@
       <c r="I11" s="3">
         <v>34</v>
       </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="K11" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>19</v>
       </c>
@@ -42305,9 +43909,14 @@
       <c r="I12" s="3">
         <v>27</v>
       </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="K12" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
@@ -42320,8 +43929,9 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" s="100"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -42349,9 +43959,14 @@
       <c r="I14" s="3">
         <v>30</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K14" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -42379,9 +43994,14 @@
       <c r="I15" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="K15" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>27</v>
       </c>
@@ -42409,9 +44029,14 @@
       <c r="I16" s="3">
         <v>37</v>
       </c>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="K16" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>68</v>
       </c>
@@ -42424,8 +44049,9 @@
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="100"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>738</v>
       </c>
@@ -42456,8 +44082,11 @@
       <c r="J18" s="8" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K18" s="103" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>40</v>
       </c>
@@ -42488,8 +44117,11 @@
       <c r="J19" s="3" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K19" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>117</v>
       </c>
@@ -42520,8 +44152,11 @@
       <c r="J20" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>141</v>
       </c>
@@ -42552,8 +44187,11 @@
       <c r="J21" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" s="103" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>739</v>
       </c>
@@ -42584,8 +44222,11 @@
       <c r="J22" s="3" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K22" s="96" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>67</v>
       </c>
@@ -42598,8 +44239,9 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23" s="100"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>42</v>
       </c>
@@ -42627,9 +44269,14 @@
       <c r="I24" s="3">
         <v>21</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K24" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>43</v>
       </c>
@@ -42657,9 +44304,14 @@
       <c r="I25" s="3">
         <v>30</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>44</v>
       </c>
@@ -42687,9 +44339,14 @@
       <c r="I26" s="3">
         <v>30</v>
       </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K26" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>45</v>
       </c>
@@ -42717,9 +44374,14 @@
       <c r="I27" s="3">
         <v>37</v>
       </c>
-      <c r="J27" s="3"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="K27" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>46</v>
       </c>
@@ -42747,9 +44409,14 @@
       <c r="I28" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K28" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>66</v>
       </c>
@@ -42762,8 +44429,9 @@
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="100"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>52</v>
       </c>
@@ -42794,8 +44462,11 @@
       <c r="J30" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="103" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>53</v>
       </c>
@@ -42826,8 +44497,11 @@
       <c r="J31" s="8" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>54</v>
       </c>
@@ -42858,8 +44532,11 @@
       <c r="J32" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>71</v>
       </c>
@@ -42872,8 +44549,9 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="100"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>60</v>
       </c>
@@ -42904,8 +44582,11 @@
       <c r="J34" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K34" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>61</v>
       </c>
@@ -42936,11 +44617,14 @@
       <c r="J35" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K35" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="18"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="18"/>
     </row>
   </sheetData>
@@ -42950,7 +44634,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28FB9D3-4430-4234-867B-100C89BF2308}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -42963,9 +44647,10 @@
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="86.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>150</v>
       </c>
@@ -42996,8 +44681,11 @@
       <c r="J1" s="26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="26" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>9</v>
       </c>
@@ -43010,8 +44698,9 @@
       <c r="H2" s="27"/>
       <c r="I2" s="27"/>
       <c r="J2" s="27"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="27"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>69</v>
       </c>
@@ -43024,8 +44713,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>10</v>
       </c>
@@ -43056,8 +44746,11 @@
       <c r="J4" s="8">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>11</v>
       </c>
@@ -43088,8 +44781,11 @@
       <c r="J5" s="8">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>70</v>
       </c>
@@ -43102,8 +44798,9 @@
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="100"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>16</v>
       </c>
@@ -43131,9 +44828,14 @@
       <c r="I7" s="3">
         <v>26</v>
       </c>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="K7" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>17</v>
       </c>
@@ -43161,9 +44863,14 @@
       <c r="I8" s="3">
         <v>17</v>
       </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K8" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
         <v>18</v>
       </c>
@@ -43191,9 +44898,14 @@
       <c r="I9" s="3">
         <v>21</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K9" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>19</v>
       </c>
@@ -43221,9 +44933,14 @@
       <c r="I10" s="3">
         <v>24</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="K10" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>24</v>
       </c>
@@ -43236,8 +44953,9 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="100"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>25</v>
       </c>
@@ -43265,9 +44983,14 @@
       <c r="I12" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K12" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="25" t="s">
         <v>26</v>
       </c>
@@ -43295,9 +45018,14 @@
       <c r="I13" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K13" s="96" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>27</v>
       </c>
@@ -43325,9 +45053,14 @@
       <c r="I14" s="3">
         <v>34</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K14" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>68</v>
       </c>
@@ -43340,8 +45073,9 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="100"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>162</v>
       </c>
@@ -43372,8 +45106,11 @@
       <c r="J16" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="103" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>161</v>
       </c>
@@ -43404,8 +45141,11 @@
       <c r="J17" s="3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>40</v>
       </c>
@@ -43433,9 +45173,14 @@
       <c r="I18" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K18" s="96" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>117</v>
       </c>
@@ -43463,9 +45208,14 @@
       <c r="I19" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J19" s="24"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="24">
+        <v>0.01</v>
+      </c>
+      <c r="K19" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>141</v>
       </c>
@@ -43496,8 +45246,11 @@
       <c r="J20" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" s="96" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>67</v>
       </c>
@@ -43510,8 +45263,9 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" s="100"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>42</v>
       </c>
@@ -43539,9 +45293,14 @@
       <c r="I22" s="3">
         <v>30</v>
       </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="K22" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
         <v>43</v>
       </c>
@@ -43569,9 +45328,14 @@
       <c r="I23" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="K23" s="96" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
         <v>44</v>
       </c>
@@ -43599,9 +45363,14 @@
       <c r="I24" s="3">
         <v>27</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="K24" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>45</v>
       </c>
@@ -43629,9 +45398,14 @@
       <c r="I25" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>46</v>
       </c>
@@ -43660,8 +45434,11 @@
         <v>27</v>
       </c>
       <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K26" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>66</v>
       </c>
@@ -43674,8 +45451,9 @@
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" s="100"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>780</v>
       </c>
@@ -43706,8 +45484,11 @@
       <c r="J28" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
         <v>53</v>
       </c>
@@ -43735,11 +45516,14 @@
       <c r="I29" s="3">
         <v>0</v>
       </c>
-      <c r="J29" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J29" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K29" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
         <v>54</v>
       </c>
@@ -43767,11 +45551,14 @@
       <c r="I30" s="3">
         <v>0</v>
       </c>
-      <c r="J30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J30" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K30" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>71</v>
       </c>
@@ -43784,8 +45571,9 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="100"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>60</v>
       </c>
@@ -43816,8 +45604,11 @@
       <c r="J32" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
         <v>61</v>
       </c>
@@ -43848,8 +45639,11 @@
       <c r="J33" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -43860,7 +45654,7 @@
       <c r="I34" s="3"/>
       <c r="J34" s="8"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -43879,7 +45673,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAE711FC-3E09-4BFD-BAFE-58741260D3F5}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -43892,9 +45686,10 @@
     <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="49.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>181</v>
       </c>
@@ -43925,8 +45720,11 @@
       <c r="J1" s="31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="31" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>9</v>
       </c>
@@ -43939,8 +45737,9 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="32"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>69</v>
       </c>
@@ -43953,8 +45752,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
         <v>10</v>
       </c>
@@ -43985,8 +45785,11 @@
       <c r="J4" s="8">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
         <v>11</v>
       </c>
@@ -44014,11 +45817,14 @@
       <c r="I5">
         <v>9</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="8">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
         <v>116</v>
       </c>
@@ -44046,11 +45852,14 @@
       <c r="I6">
         <v>11</v>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="8">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
         <v>182</v>
       </c>
@@ -44081,8 +45890,11 @@
       <c r="J7" s="8">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>70</v>
       </c>
@@ -44095,8 +45907,9 @@
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="100"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
         <v>16</v>
       </c>
@@ -44124,9 +45937,14 @@
       <c r="I9" s="3">
         <v>22</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="K9" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
         <v>17</v>
       </c>
@@ -44154,9 +45972,14 @@
       <c r="I10" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K10" s="96" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
         <v>18</v>
       </c>
@@ -44184,9 +46007,14 @@
       <c r="I11" s="3">
         <v>26</v>
       </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="K11" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="30" t="s">
         <v>19</v>
       </c>
@@ -44214,9 +46042,14 @@
       <c r="I12" s="3">
         <v>24</v>
       </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="K12" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
@@ -44229,8 +46062,9 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" s="100"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
         <v>25</v>
       </c>
@@ -44258,9 +46092,14 @@
       <c r="I14" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="96" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
         <v>26</v>
       </c>
@@ -44288,9 +46127,14 @@
       <c r="I15" s="3">
         <v>32</v>
       </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="K15" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="30" t="s">
         <v>27</v>
       </c>
@@ -44318,9 +46162,14 @@
       <c r="I16" s="3">
         <v>34</v>
       </c>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K16" s="96" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>68</v>
       </c>
@@ -44333,8 +46182,9 @@
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="100"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="30" t="s">
         <v>31</v>
       </c>
@@ -44362,9 +46212,14 @@
       <c r="I18" s="3">
         <v>43</v>
       </c>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K18" s="103" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
         <v>40</v>
       </c>
@@ -44392,9 +46247,14 @@
       <c r="I19" s="3">
         <v>0</v>
       </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="K19" s="96" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
         <v>117</v>
       </c>
@@ -44422,9 +46282,14 @@
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="K20" s="96" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="30" t="s">
         <v>35</v>
       </c>
@@ -44452,9 +46317,14 @@
       <c r="I21" s="3">
         <v>29</v>
       </c>
-      <c r="J21" s="24"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J21" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="K21" s="103" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="30" t="s">
         <v>36</v>
       </c>
@@ -44482,8 +46352,14 @@
       <c r="I22" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K22" s="96" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>67</v>
       </c>
@@ -44496,8 +46372,9 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23" s="100"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="30" t="s">
         <v>42</v>
       </c>
@@ -44525,9 +46402,14 @@
       <c r="I24" s="3">
         <v>30</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="K24" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
         <v>43</v>
       </c>
@@ -44555,9 +46437,14 @@
       <c r="I25" s="3">
         <v>30</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="30" t="s">
         <v>44</v>
       </c>
@@ -44585,9 +46472,14 @@
       <c r="I26" s="3">
         <v>27</v>
       </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="K26" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="30" t="s">
         <v>45</v>
       </c>
@@ -44615,9 +46507,14 @@
       <c r="I27" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="J27" s="3"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="K27" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="30" t="s">
         <v>46</v>
       </c>
@@ -44645,9 +46542,14 @@
       <c r="I28" s="3">
         <v>30</v>
       </c>
-      <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K28" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>66</v>
       </c>
@@ -44660,8 +46562,9 @@
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="100"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="30" t="s">
         <v>52</v>
       </c>
@@ -44692,8 +46595,11 @@
       <c r="J30" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="30" t="s">
         <v>53</v>
       </c>
@@ -44724,8 +46630,11 @@
       <c r="J31" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="30" t="s">
         <v>54</v>
       </c>
@@ -44756,8 +46665,11 @@
       <c r="J32" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>71</v>
       </c>
@@ -44770,8 +46682,9 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="100"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="30" t="s">
         <v>60</v>
       </c>
@@ -44799,11 +46712,14 @@
       <c r="I34" s="3">
         <v>0</v>
       </c>
-      <c r="J34" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J34" s="8">
+        <v>0</v>
+      </c>
+      <c r="K34" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="30" t="s">
         <v>61</v>
       </c>
@@ -44831,8 +46747,11 @@
       <c r="I35" s="3">
         <v>0</v>
       </c>
-      <c r="J35" s="24">
-        <v>0</v>
+      <c r="J35" s="8">
+        <v>0</v>
+      </c>
+      <c r="K35" s="102" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -44842,7 +46761,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDF2568-BC15-444A-922F-A5056E2E07DE}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -44855,9 +46774,10 @@
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="42.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="48" t="s">
         <v>374</v>
       </c>
@@ -44888,8 +46808,11 @@
       <c r="J1" s="31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="31" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
         <v>9</v>
       </c>
@@ -44902,8 +46825,9 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="32"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>69</v>
       </c>
@@ -44916,8 +46840,9 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="48" t="s">
         <v>10</v>
       </c>
@@ -44948,8 +46873,11 @@
       <c r="J4" s="8" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="102" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>70</v>
       </c>
@@ -44962,8 +46890,9 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="100"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="48" t="s">
         <v>16</v>
       </c>
@@ -44991,9 +46920,14 @@
       <c r="I6" s="3">
         <v>22</v>
       </c>
-      <c r="J6" s="3"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J6" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="K6" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="48" t="s">
         <v>17</v>
       </c>
@@ -45021,9 +46955,14 @@
       <c r="I7" s="3">
         <v>40</v>
       </c>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="K7" s="96" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="48" t="s">
         <v>18</v>
       </c>
@@ -45051,9 +46990,14 @@
       <c r="I8" s="3">
         <v>29</v>
       </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K8" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="48" t="s">
         <v>19</v>
       </c>
@@ -45081,9 +47025,14 @@
       <c r="I9" s="3">
         <v>29</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="K9" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>24</v>
       </c>
@@ -45096,8 +47045,9 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10" s="100"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="48" t="s">
         <v>25</v>
       </c>
@@ -45125,9 +47075,14 @@
       <c r="I11" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K11" s="96" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
         <v>26</v>
       </c>
@@ -45155,9 +47110,14 @@
       <c r="I12" s="3">
         <v>30</v>
       </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="48" t="s">
         <v>27</v>
       </c>
@@ -45185,9 +47145,14 @@
       <c r="I13" s="3">
         <v>40</v>
       </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K13" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>68</v>
       </c>
@@ -45200,8 +47165,9 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K14" s="100"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="48" t="s">
         <v>31</v>
       </c>
@@ -45229,9 +47195,14 @@
       <c r="I15" s="3">
         <v>55</v>
       </c>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="8" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K15" s="103" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="48" t="s">
         <v>40</v>
       </c>
@@ -45259,9 +47230,14 @@
       <c r="I16" s="3">
         <v>0</v>
       </c>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="K16" s="96" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="48" t="s">
         <v>117</v>
       </c>
@@ -45289,9 +47265,14 @@
       <c r="I17" s="3">
         <v>0</v>
       </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="K17" s="96" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="48" t="s">
         <v>35</v>
       </c>
@@ -45319,9 +47300,14 @@
       <c r="I18" s="3">
         <v>29</v>
       </c>
-      <c r="J18" s="24"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="K18" s="102" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="48" t="s">
         <v>36</v>
       </c>
@@ -45349,8 +47335,14 @@
       <c r="I19" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="K19" s="96" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>67</v>
       </c>
@@ -45363,8 +47355,9 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" s="100"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="48" t="s">
         <v>42</v>
       </c>
@@ -45392,9 +47385,14 @@
       <c r="I21" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J21" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="K21" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="48" t="s">
         <v>43</v>
       </c>
@@ -45422,9 +47420,14 @@
       <c r="I22" s="3">
         <v>30</v>
       </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K22" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="48" t="s">
         <v>44</v>
       </c>
@@ -45452,9 +47455,14 @@
       <c r="I23" s="3">
         <v>37</v>
       </c>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="K23" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="48" t="s">
         <v>45</v>
       </c>
@@ -45482,9 +47490,14 @@
       <c r="I24" s="3">
         <v>34</v>
       </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K24" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="48" t="s">
         <v>46</v>
       </c>
@@ -45512,9 +47525,14 @@
       <c r="I25" s="3">
         <v>32</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="K25" s="96" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>66</v>
       </c>
@@ -45527,8 +47545,9 @@
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K26" s="100"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="48" t="s">
         <v>52</v>
       </c>
@@ -45559,8 +47578,11 @@
       <c r="J27" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="48" t="s">
         <v>53</v>
       </c>
@@ -45591,8 +47613,11 @@
       <c r="J28" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="48" t="s">
         <v>54</v>
       </c>
@@ -45623,8 +47648,11 @@
       <c r="J29" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="97" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>71</v>
       </c>
@@ -45637,8 +47665,9 @@
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="100"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="48" t="s">
         <v>60</v>
       </c>
@@ -45669,8 +47698,11 @@
       <c r="J31" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="102" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="48" t="s">
         <v>61</v>
       </c>
@@ -45700,6 +47732,9 @@
       </c>
       <c r="J32" s="24">
         <v>0</v>
+      </c>
+      <c r="K32" s="102" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>
